--- a/CardData/BuffCard.xlsx
+++ b/CardData/BuffCard.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>1791892074593934</author>
+    <author>1792414558057962</author>
   </authors>
   <commentList>
     <comment ref="E3" authorId="0">
@@ -55,9 +55,18 @@
     <t>duration</t>
   </si>
   <si>
+    <t>discription</t>
+  </si>
+  <si>
+    <t>starteffect</t>
+  </si>
+  <si>
     <t>effect</t>
   </si>
   <si>
+    <t>endeffect</t>
+  </si>
+  <si>
     <t>owner</t>
   </si>
   <si>
@@ -82,6 +91,15 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=_),int</t>
+  </si>
+  <si>
+    <t>(array#sep=_),int</t>
+  </si>
+  <si>
+    <t>(array#sep=_),int</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -103,21 +121,36 @@
     <t>持续时间</t>
   </si>
   <si>
-    <t>卡牌效果</t>
+    <t>卡牌效果描述</t>
+  </si>
+  <si>
+    <t>展开时效果</t>
+  </si>
+  <si>
+    <t>展开中效果</t>
+  </si>
+  <si>
+    <t>弃置时效果</t>
   </si>
   <si>
     <t>所属</t>
   </si>
   <si>
     <t>燃心</t>
-  </si>
-  <si>
-    <t>无</t>
   </si>
   <si>
     <t xml:space="preserve">使用时，我方能量+1
 我方主要阶段结束时，将一张能量加入手牌。
 若处于【连击】状态，再将一张能量加入手牌。</t>
+  </si>
+  <si>
+    <t>1_1_0</t>
+  </si>
+  <si>
+    <t>5_1_13_1_0</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
   <si>
     <t>c_0</t>
@@ -130,7 +163,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -144,46 +177,62 @@
       <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="宋体"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="BlinkMacSystemFont"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="宋体"/>
       <sz val="11"/>
     </font>
-    <font>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="D7D8D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
   </borders>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf fontId="1" applyFont="1">
+    <xf fontId="1" fillId="2" applyFont="1" applyFill="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="164" fontId="1" fillId="2" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf fontId="2" applyFont="1">
+    <xf fontId="2" fillId="2" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="2" applyFont="1" applyFill="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="2" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="164" fontId="3" fillId="2" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf fontId="3" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf fontId="5" applyFont="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" applyFont="1">
+    <xf fontId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -197,9 +246,10 @@
     <col min="1" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="15.958333" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="19" width="10" customWidth="1"/>
+    <col min="7" max="7" width="41.958332" customWidth="1"/>
+    <col min="8" max="10" width="16.175001" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="22" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -221,678 +271,1335 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="C3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+    </row>
+    <row r="4" ht="38.545456" customHeight="1">
+      <c r="A4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="B4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>27</v>
+      <c r="G4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5">
-      <c r="E5" s="6"/>
+      <c r="E5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6">
-      <c r="E6" s="6"/>
+      <c r="E6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
     </row>
     <row r="7">
-      <c r="E7" s="6"/>
+      <c r="E7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8">
-      <c r="E8" s="6"/>
+      <c r="E8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
     </row>
     <row r="9">
-      <c r="E9" s="6"/>
+      <c r="E9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10">
-      <c r="E10" s="6"/>
+      <c r="E10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
     </row>
     <row r="11">
-      <c r="E11" s="6"/>
+      <c r="E11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12">
-      <c r="E12" s="6"/>
+      <c r="E12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13">
-      <c r="E13" s="6"/>
+      <c r="E13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14">
-      <c r="E14" s="6"/>
+      <c r="E14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
     </row>
     <row r="15">
-      <c r="E15" s="6"/>
+      <c r="E15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16">
-      <c r="E16" s="6"/>
+      <c r="E16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
     </row>
     <row r="17">
-      <c r="E17" s="6"/>
+      <c r="E17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18">
-      <c r="E18" s="6"/>
+      <c r="E18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
     </row>
     <row r="19">
-      <c r="E19" s="6"/>
+      <c r="E19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="20">
-      <c r="E20" s="6"/>
+      <c r="E20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
     </row>
     <row r="21">
-      <c r="E21" s="6"/>
+      <c r="E21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
     </row>
     <row r="22">
-      <c r="E22" s="6"/>
+      <c r="E22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
     </row>
     <row r="23">
-      <c r="E23" s="6"/>
+      <c r="E23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
     </row>
     <row r="24">
-      <c r="E24" s="6"/>
+      <c r="E24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25">
-      <c r="E25" s="6"/>
+      <c r="E25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
     </row>
     <row r="26">
-      <c r="E26" s="6"/>
+      <c r="E26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="27">
-      <c r="E27" s="6"/>
+      <c r="E27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
     </row>
     <row r="28">
-      <c r="E28" s="6"/>
+      <c r="E28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29">
-      <c r="E29" s="6"/>
+      <c r="E29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
     </row>
     <row r="30">
-      <c r="E30" s="6"/>
+      <c r="E30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31">
-      <c r="E31" s="6"/>
+      <c r="E31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
     </row>
     <row r="32">
-      <c r="E32" s="6"/>
+      <c r="E32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33">
-      <c r="E33" s="6"/>
+      <c r="E33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
     </row>
     <row r="34">
-      <c r="E34" s="6"/>
+      <c r="E34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
     </row>
     <row r="35">
-      <c r="E35" s="6"/>
+      <c r="E35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
     </row>
     <row r="36">
-      <c r="E36" s="6"/>
+      <c r="E36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37">
-      <c r="E37" s="6"/>
+      <c r="E37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
     </row>
     <row r="38">
-      <c r="E38" s="6"/>
+      <c r="E38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
     </row>
     <row r="39">
-      <c r="E39" s="6"/>
+      <c r="E39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
     </row>
     <row r="40">
-      <c r="E40" s="6"/>
+      <c r="E40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
     </row>
     <row r="41">
-      <c r="E41" s="6"/>
+      <c r="E41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
     </row>
     <row r="42">
-      <c r="E42" s="6"/>
+      <c r="E42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
     </row>
     <row r="43">
-      <c r="E43" s="6"/>
+      <c r="E43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
     </row>
     <row r="44">
-      <c r="E44" s="6"/>
+      <c r="E44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
     </row>
     <row r="45">
-      <c r="E45" s="6"/>
+      <c r="E45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
     </row>
     <row r="46">
-      <c r="E46" s="6"/>
+      <c r="E46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
     </row>
     <row r="47">
-      <c r="E47" s="6"/>
+      <c r="E47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
     </row>
     <row r="48">
-      <c r="E48" s="6"/>
+      <c r="E48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
     </row>
     <row r="49">
-      <c r="E49" s="6"/>
+      <c r="E49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
     </row>
     <row r="50">
-      <c r="E50" s="6"/>
+      <c r="E50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
     </row>
     <row r="51">
-      <c r="E51" s="6"/>
+      <c r="E51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
     </row>
     <row r="52">
-      <c r="E52" s="6"/>
+      <c r="E52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
     </row>
     <row r="53">
-      <c r="E53" s="6"/>
+      <c r="E53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
     </row>
     <row r="54">
-      <c r="E54" s="6"/>
+      <c r="E54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
     </row>
     <row r="55">
-      <c r="E55" s="6"/>
+      <c r="E55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
     </row>
     <row r="56">
-      <c r="E56" s="6"/>
+      <c r="E56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
     </row>
     <row r="57">
-      <c r="E57" s="6"/>
+      <c r="E57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
     </row>
     <row r="58">
-      <c r="E58" s="6"/>
+      <c r="E58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
     </row>
     <row r="59">
-      <c r="E59" s="6"/>
+      <c r="E59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
     </row>
     <row r="60">
-      <c r="E60" s="6"/>
+      <c r="E60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
     </row>
     <row r="61">
-      <c r="E61" s="6"/>
+      <c r="E61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
     </row>
     <row r="62">
-      <c r="E62" s="6"/>
+      <c r="E62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
     </row>
     <row r="63">
-      <c r="E63" s="6"/>
+      <c r="E63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
     </row>
     <row r="64">
-      <c r="E64" s="6"/>
+      <c r="E64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
     </row>
     <row r="65">
-      <c r="E65" s="6"/>
+      <c r="E65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
     </row>
     <row r="66">
-      <c r="E66" s="6"/>
+      <c r="E66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="9"/>
     </row>
     <row r="67">
-      <c r="E67" s="6"/>
+      <c r="E67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
     </row>
     <row r="68">
-      <c r="E68" s="6"/>
+      <c r="E68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
     </row>
     <row r="69">
-      <c r="E69" s="6"/>
+      <c r="E69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
     </row>
     <row r="70">
-      <c r="E70" s="6"/>
+      <c r="E70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
     </row>
     <row r="71">
-      <c r="E71" s="6"/>
+      <c r="E71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
     </row>
     <row r="72">
-      <c r="E72" s="6"/>
+      <c r="E72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9"/>
     </row>
     <row r="73">
-      <c r="E73" s="6"/>
+      <c r="E73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
     </row>
     <row r="74">
-      <c r="E74" s="6"/>
+      <c r="E74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="9"/>
     </row>
     <row r="75">
-      <c r="E75" s="6"/>
+      <c r="E75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
     </row>
     <row r="76">
-      <c r="E76" s="6"/>
+      <c r="E76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
     </row>
     <row r="77">
-      <c r="E77" s="6"/>
+      <c r="E77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
     </row>
     <row r="78">
-      <c r="E78" s="6"/>
+      <c r="E78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
     </row>
     <row r="79">
-      <c r="E79" s="6"/>
+      <c r="E79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
     </row>
     <row r="80">
-      <c r="E80" s="6"/>
+      <c r="E80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="9"/>
     </row>
     <row r="81">
-      <c r="E81" s="6"/>
+      <c r="E81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
     </row>
     <row r="82">
-      <c r="E82" s="6"/>
+      <c r="E82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
     </row>
     <row r="83">
-      <c r="E83" s="6"/>
+      <c r="E83" s="9"/>
+      <c r="G83" s="9"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="9"/>
     </row>
     <row r="84">
-      <c r="E84" s="6"/>
+      <c r="E84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="I84" s="9"/>
+      <c r="J84" s="9"/>
     </row>
     <row r="85">
-      <c r="E85" s="6"/>
+      <c r="E85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
     </row>
     <row r="86">
-      <c r="E86" s="6"/>
+      <c r="E86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9"/>
     </row>
     <row r="87">
-      <c r="E87" s="6"/>
+      <c r="E87" s="9"/>
+      <c r="G87" s="9"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="9"/>
     </row>
     <row r="88">
-      <c r="E88" s="6"/>
+      <c r="E88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="9"/>
     </row>
     <row r="89">
-      <c r="E89" s="6"/>
+      <c r="E89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="9"/>
     </row>
     <row r="90">
-      <c r="E90" s="6"/>
+      <c r="E90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="9"/>
     </row>
     <row r="91">
-      <c r="E91" s="6"/>
+      <c r="E91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="9"/>
     </row>
     <row r="92">
-      <c r="E92" s="6"/>
+      <c r="E92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="9"/>
     </row>
     <row r="93">
-      <c r="E93" s="6"/>
+      <c r="E93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="9"/>
     </row>
     <row r="94">
-      <c r="E94" s="6"/>
+      <c r="E94" s="9"/>
+      <c r="G94" s="9"/>
+      <c r="I94" s="9"/>
+      <c r="J94" s="9"/>
     </row>
     <row r="95">
-      <c r="E95" s="6"/>
+      <c r="E95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="9"/>
     </row>
     <row r="96">
-      <c r="E96" s="6"/>
+      <c r="E96" s="9"/>
+      <c r="G96" s="9"/>
+      <c r="I96" s="9"/>
+      <c r="J96" s="9"/>
     </row>
     <row r="97">
-      <c r="E97" s="6"/>
+      <c r="E97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9"/>
     </row>
     <row r="98">
-      <c r="E98" s="6"/>
+      <c r="E98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="9"/>
     </row>
     <row r="99">
-      <c r="E99" s="6"/>
+      <c r="E99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="9"/>
     </row>
     <row r="100">
-      <c r="E100" s="6"/>
+      <c r="E100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="9"/>
     </row>
     <row r="101">
-      <c r="E101" s="6"/>
+      <c r="E101" s="9"/>
+      <c r="G101" s="9"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="9"/>
     </row>
     <row r="102">
-      <c r="E102" s="6"/>
+      <c r="E102" s="9"/>
+      <c r="G102" s="9"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="9"/>
     </row>
     <row r="103">
-      <c r="E103" s="6"/>
+      <c r="E103" s="9"/>
+      <c r="G103" s="9"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="9"/>
     </row>
     <row r="104">
-      <c r="E104" s="6"/>
+      <c r="E104" s="9"/>
+      <c r="G104" s="9"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="9"/>
     </row>
     <row r="105">
-      <c r="E105" s="6"/>
+      <c r="E105" s="9"/>
+      <c r="G105" s="9"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="9"/>
     </row>
     <row r="106">
-      <c r="E106" s="6"/>
+      <c r="E106" s="9"/>
+      <c r="G106" s="9"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="9"/>
     </row>
     <row r="107">
-      <c r="E107" s="6"/>
+      <c r="E107" s="9"/>
+      <c r="G107" s="9"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="9"/>
     </row>
     <row r="108">
-      <c r="E108" s="6"/>
+      <c r="E108" s="9"/>
+      <c r="G108" s="9"/>
+      <c r="I108" s="9"/>
+      <c r="J108" s="9"/>
     </row>
     <row r="109">
-      <c r="E109" s="6"/>
+      <c r="E109" s="9"/>
+      <c r="G109" s="9"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="9"/>
     </row>
     <row r="110">
-      <c r="E110" s="6"/>
+      <c r="E110" s="9"/>
+      <c r="G110" s="9"/>
+      <c r="I110" s="9"/>
+      <c r="J110" s="9"/>
     </row>
     <row r="111">
-      <c r="E111" s="6"/>
+      <c r="E111" s="9"/>
+      <c r="G111" s="9"/>
+      <c r="I111" s="9"/>
+      <c r="J111" s="9"/>
     </row>
     <row r="112">
-      <c r="E112" s="6"/>
+      <c r="E112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="9"/>
     </row>
     <row r="113">
-      <c r="E113" s="6"/>
+      <c r="E113" s="9"/>
+      <c r="G113" s="9"/>
+      <c r="I113" s="9"/>
+      <c r="J113" s="9"/>
     </row>
     <row r="114">
-      <c r="E114" s="6"/>
+      <c r="E114" s="9"/>
+      <c r="G114" s="9"/>
+      <c r="I114" s="9"/>
+      <c r="J114" s="9"/>
     </row>
     <row r="115">
-      <c r="E115" s="6"/>
+      <c r="E115" s="9"/>
+      <c r="G115" s="9"/>
+      <c r="I115" s="9"/>
+      <c r="J115" s="9"/>
     </row>
     <row r="116">
-      <c r="E116" s="6"/>
+      <c r="E116" s="9"/>
+      <c r="G116" s="9"/>
+      <c r="I116" s="9"/>
+      <c r="J116" s="9"/>
     </row>
     <row r="117">
-      <c r="E117" s="6"/>
+      <c r="E117" s="9"/>
+      <c r="G117" s="9"/>
+      <c r="I117" s="9"/>
+      <c r="J117" s="9"/>
     </row>
     <row r="118">
-      <c r="E118" s="6"/>
+      <c r="E118" s="9"/>
+      <c r="G118" s="9"/>
+      <c r="I118" s="9"/>
+      <c r="J118" s="9"/>
     </row>
     <row r="119">
-      <c r="E119" s="6"/>
+      <c r="E119" s="9"/>
+      <c r="G119" s="9"/>
+      <c r="I119" s="9"/>
+      <c r="J119" s="9"/>
     </row>
     <row r="120">
-      <c r="E120" s="6"/>
+      <c r="E120" s="9"/>
+      <c r="G120" s="9"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="9"/>
     </row>
     <row r="121">
-      <c r="E121" s="6"/>
+      <c r="E121" s="9"/>
+      <c r="G121" s="9"/>
+      <c r="I121" s="9"/>
+      <c r="J121" s="9"/>
     </row>
     <row r="122">
-      <c r="E122" s="6"/>
+      <c r="E122" s="9"/>
+      <c r="G122" s="9"/>
+      <c r="I122" s="9"/>
+      <c r="J122" s="9"/>
     </row>
     <row r="123">
-      <c r="E123" s="6"/>
+      <c r="E123" s="9"/>
+      <c r="G123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
     </row>
     <row r="124">
-      <c r="E124" s="6"/>
+      <c r="E124" s="9"/>
+      <c r="G124" s="9"/>
+      <c r="I124" s="9"/>
+      <c r="J124" s="9"/>
     </row>
     <row r="125">
-      <c r="E125" s="6"/>
+      <c r="E125" s="9"/>
+      <c r="G125" s="9"/>
+      <c r="I125" s="9"/>
+      <c r="J125" s="9"/>
     </row>
     <row r="126">
-      <c r="E126" s="6"/>
+      <c r="E126" s="9"/>
+      <c r="G126" s="9"/>
+      <c r="I126" s="9"/>
+      <c r="J126" s="9"/>
     </row>
     <row r="127">
-      <c r="E127" s="6"/>
+      <c r="E127" s="9"/>
+      <c r="G127" s="9"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="9"/>
     </row>
     <row r="128">
-      <c r="E128" s="6"/>
+      <c r="E128" s="9"/>
+      <c r="G128" s="9"/>
+      <c r="I128" s="9"/>
+      <c r="J128" s="9"/>
     </row>
     <row r="129">
-      <c r="E129" s="6"/>
+      <c r="E129" s="9"/>
+      <c r="G129" s="9"/>
+      <c r="I129" s="9"/>
+      <c r="J129" s="9"/>
     </row>
     <row r="130">
-      <c r="E130" s="6"/>
+      <c r="E130" s="9"/>
+      <c r="G130" s="9"/>
+      <c r="I130" s="9"/>
+      <c r="J130" s="9"/>
     </row>
     <row r="131">
-      <c r="E131" s="6"/>
+      <c r="E131" s="9"/>
+      <c r="G131" s="9"/>
+      <c r="I131" s="9"/>
+      <c r="J131" s="9"/>
     </row>
     <row r="132">
-      <c r="E132" s="6"/>
+      <c r="E132" s="9"/>
+      <c r="G132" s="9"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="9"/>
     </row>
     <row r="133">
-      <c r="E133" s="6"/>
+      <c r="E133" s="9"/>
+      <c r="G133" s="9"/>
+      <c r="I133" s="9"/>
+      <c r="J133" s="9"/>
     </row>
     <row r="134">
-      <c r="E134" s="6"/>
+      <c r="E134" s="9"/>
+      <c r="G134" s="9"/>
+      <c r="I134" s="9"/>
+      <c r="J134" s="9"/>
     </row>
     <row r="135">
-      <c r="E135" s="6"/>
+      <c r="E135" s="9"/>
+      <c r="G135" s="9"/>
+      <c r="I135" s="9"/>
+      <c r="J135" s="9"/>
     </row>
     <row r="136">
-      <c r="E136" s="6"/>
+      <c r="E136" s="9"/>
+      <c r="G136" s="9"/>
+      <c r="I136" s="9"/>
+      <c r="J136" s="9"/>
     </row>
     <row r="137">
-      <c r="E137" s="6"/>
+      <c r="E137" s="9"/>
+      <c r="G137" s="9"/>
+      <c r="I137" s="9"/>
+      <c r="J137" s="9"/>
     </row>
     <row r="138">
-      <c r="E138" s="6"/>
+      <c r="E138" s="9"/>
+      <c r="G138" s="9"/>
+      <c r="I138" s="9"/>
+      <c r="J138" s="9"/>
     </row>
     <row r="139">
-      <c r="E139" s="6"/>
+      <c r="E139" s="9"/>
+      <c r="G139" s="9"/>
+      <c r="I139" s="9"/>
+      <c r="J139" s="9"/>
     </row>
     <row r="140">
-      <c r="E140" s="6"/>
+      <c r="E140" s="9"/>
+      <c r="G140" s="9"/>
+      <c r="I140" s="9"/>
+      <c r="J140" s="9"/>
     </row>
     <row r="141">
-      <c r="E141" s="6"/>
+      <c r="E141" s="9"/>
+      <c r="G141" s="9"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="9"/>
     </row>
     <row r="142">
-      <c r="E142" s="6"/>
+      <c r="E142" s="9"/>
+      <c r="G142" s="9"/>
+      <c r="I142" s="9"/>
+      <c r="J142" s="9"/>
     </row>
     <row r="143">
-      <c r="E143" s="6"/>
+      <c r="E143" s="9"/>
+      <c r="G143" s="9"/>
+      <c r="I143" s="9"/>
+      <c r="J143" s="9"/>
     </row>
     <row r="144">
-      <c r="E144" s="6"/>
+      <c r="E144" s="9"/>
+      <c r="G144" s="9"/>
+      <c r="I144" s="9"/>
+      <c r="J144" s="9"/>
     </row>
     <row r="145">
-      <c r="E145" s="6"/>
+      <c r="E145" s="9"/>
+      <c r="G145" s="9"/>
+      <c r="I145" s="9"/>
+      <c r="J145" s="9"/>
     </row>
     <row r="146">
-      <c r="E146" s="6"/>
+      <c r="E146" s="9"/>
+      <c r="G146" s="9"/>
+      <c r="I146" s="9"/>
+      <c r="J146" s="9"/>
     </row>
     <row r="147">
-      <c r="E147" s="6"/>
+      <c r="E147" s="9"/>
+      <c r="G147" s="9"/>
+      <c r="I147" s="9"/>
+      <c r="J147" s="9"/>
     </row>
     <row r="148">
-      <c r="E148" s="6"/>
+      <c r="E148" s="9"/>
+      <c r="G148" s="9"/>
+      <c r="I148" s="9"/>
+      <c r="J148" s="9"/>
     </row>
     <row r="149">
-      <c r="E149" s="6"/>
+      <c r="E149" s="9"/>
+      <c r="G149" s="9"/>
+      <c r="I149" s="9"/>
+      <c r="J149" s="9"/>
     </row>
     <row r="150">
-      <c r="E150" s="6"/>
+      <c r="E150" s="9"/>
+      <c r="G150" s="9"/>
+      <c r="I150" s="9"/>
+      <c r="J150" s="9"/>
     </row>
     <row r="151">
-      <c r="E151" s="6"/>
+      <c r="E151" s="9"/>
+      <c r="G151" s="9"/>
+      <c r="I151" s="9"/>
+      <c r="J151" s="9"/>
     </row>
     <row r="152">
-      <c r="E152" s="6"/>
+      <c r="E152" s="9"/>
+      <c r="G152" s="9"/>
+      <c r="I152" s="9"/>
+      <c r="J152" s="9"/>
     </row>
     <row r="153">
-      <c r="E153" s="6"/>
+      <c r="E153" s="9"/>
+      <c r="G153" s="9"/>
+      <c r="I153" s="9"/>
+      <c r="J153" s="9"/>
     </row>
     <row r="154">
-      <c r="E154" s="6"/>
+      <c r="E154" s="9"/>
+      <c r="G154" s="9"/>
+      <c r="I154" s="9"/>
+      <c r="J154" s="9"/>
     </row>
     <row r="155">
-      <c r="E155" s="6"/>
+      <c r="E155" s="9"/>
+      <c r="G155" s="9"/>
+      <c r="I155" s="9"/>
+      <c r="J155" s="9"/>
     </row>
     <row r="156">
-      <c r="E156" s="6"/>
+      <c r="E156" s="9"/>
+      <c r="G156" s="9"/>
+      <c r="I156" s="9"/>
+      <c r="J156" s="9"/>
     </row>
     <row r="157">
-      <c r="E157" s="6"/>
+      <c r="E157" s="9"/>
+      <c r="G157" s="9"/>
+      <c r="I157" s="9"/>
+      <c r="J157" s="9"/>
     </row>
     <row r="158">
-      <c r="E158" s="6"/>
+      <c r="E158" s="9"/>
+      <c r="G158" s="9"/>
+      <c r="I158" s="9"/>
+      <c r="J158" s="9"/>
     </row>
     <row r="159">
-      <c r="E159" s="6"/>
+      <c r="E159" s="9"/>
+      <c r="G159" s="9"/>
+      <c r="I159" s="9"/>
+      <c r="J159" s="9"/>
     </row>
     <row r="160">
-      <c r="E160" s="6"/>
+      <c r="E160" s="9"/>
+      <c r="G160" s="9"/>
+      <c r="I160" s="9"/>
+      <c r="J160" s="9"/>
     </row>
     <row r="161">
-      <c r="E161" s="6"/>
+      <c r="E161" s="9"/>
+      <c r="G161" s="9"/>
+      <c r="I161" s="9"/>
+      <c r="J161" s="9"/>
     </row>
     <row r="162">
-      <c r="E162" s="6"/>
+      <c r="E162" s="9"/>
+      <c r="G162" s="9"/>
+      <c r="I162" s="9"/>
+      <c r="J162" s="9"/>
     </row>
     <row r="163">
-      <c r="E163" s="6"/>
+      <c r="E163" s="9"/>
+      <c r="G163" s="9"/>
+      <c r="I163" s="9"/>
+      <c r="J163" s="9"/>
     </row>
     <row r="164">
-      <c r="E164" s="6"/>
+      <c r="E164" s="9"/>
+      <c r="G164" s="9"/>
+      <c r="I164" s="9"/>
+      <c r="J164" s="9"/>
     </row>
     <row r="165">
-      <c r="E165" s="6"/>
+      <c r="E165" s="9"/>
+      <c r="G165" s="9"/>
+      <c r="I165" s="9"/>
+      <c r="J165" s="9"/>
     </row>
     <row r="166">
-      <c r="E166" s="6"/>
+      <c r="E166" s="9"/>
+      <c r="G166" s="9"/>
+      <c r="I166" s="9"/>
+      <c r="J166" s="9"/>
     </row>
     <row r="167">
-      <c r="E167" s="6"/>
+      <c r="E167" s="9"/>
+      <c r="G167" s="9"/>
+      <c r="I167" s="9"/>
+      <c r="J167" s="9"/>
     </row>
     <row r="168">
-      <c r="E168" s="6"/>
+      <c r="E168" s="9"/>
+      <c r="G168" s="9"/>
+      <c r="I168" s="9"/>
+      <c r="J168" s="9"/>
     </row>
     <row r="169">
-      <c r="E169" s="6"/>
+      <c r="E169" s="9"/>
+      <c r="G169" s="9"/>
+      <c r="I169" s="9"/>
+      <c r="J169" s="9"/>
     </row>
     <row r="170">
-      <c r="E170" s="6"/>
+      <c r="E170" s="9"/>
+      <c r="G170" s="9"/>
+      <c r="I170" s="9"/>
+      <c r="J170" s="9"/>
     </row>
     <row r="171">
-      <c r="E171" s="6"/>
+      <c r="E171" s="9"/>
+      <c r="G171" s="9"/>
+      <c r="I171" s="9"/>
+      <c r="J171" s="9"/>
     </row>
     <row r="172">
-      <c r="E172" s="6"/>
+      <c r="E172" s="9"/>
+      <c r="G172" s="9"/>
+      <c r="I172" s="9"/>
+      <c r="J172" s="9"/>
     </row>
     <row r="173">
-      <c r="E173" s="6"/>
+      <c r="E173" s="9"/>
+      <c r="G173" s="9"/>
+      <c r="I173" s="9"/>
+      <c r="J173" s="9"/>
     </row>
     <row r="174">
-      <c r="E174" s="6"/>
+      <c r="E174" s="9"/>
+      <c r="G174" s="9"/>
+      <c r="I174" s="9"/>
+      <c r="J174" s="9"/>
     </row>
     <row r="175">
-      <c r="E175" s="6"/>
+      <c r="E175" s="9"/>
+      <c r="G175" s="9"/>
+      <c r="I175" s="9"/>
+      <c r="J175" s="9"/>
     </row>
     <row r="176">
-      <c r="E176" s="6"/>
+      <c r="E176" s="9"/>
+      <c r="G176" s="9"/>
+      <c r="I176" s="9"/>
+      <c r="J176" s="9"/>
     </row>
     <row r="177">
-      <c r="E177" s="6"/>
+      <c r="E177" s="9"/>
+      <c r="G177" s="9"/>
+      <c r="I177" s="9"/>
+      <c r="J177" s="9"/>
     </row>
     <row r="178">
-      <c r="E178" s="6"/>
+      <c r="E178" s="9"/>
+      <c r="G178" s="9"/>
+      <c r="I178" s="9"/>
+      <c r="J178" s="9"/>
     </row>
     <row r="179">
-      <c r="E179" s="6"/>
+      <c r="E179" s="9"/>
+      <c r="G179" s="9"/>
+      <c r="I179" s="9"/>
+      <c r="J179" s="9"/>
     </row>
     <row r="180">
-      <c r="E180" s="6"/>
+      <c r="E180" s="9"/>
+      <c r="G180" s="9"/>
+      <c r="I180" s="9"/>
+      <c r="J180" s="9"/>
     </row>
     <row r="181">
-      <c r="E181" s="6"/>
+      <c r="E181" s="9"/>
+      <c r="G181" s="9"/>
+      <c r="I181" s="9"/>
+      <c r="J181" s="9"/>
     </row>
     <row r="182">
-      <c r="E182" s="6"/>
+      <c r="E182" s="9"/>
+      <c r="G182" s="9"/>
+      <c r="I182" s="9"/>
+      <c r="J182" s="9"/>
     </row>
     <row r="183">
-      <c r="E183" s="6"/>
+      <c r="E183" s="9"/>
+      <c r="G183" s="9"/>
+      <c r="I183" s="9"/>
+      <c r="J183" s="9"/>
     </row>
     <row r="184">
-      <c r="E184" s="6"/>
+      <c r="E184" s="9"/>
+      <c r="G184" s="9"/>
+      <c r="I184" s="9"/>
+      <c r="J184" s="9"/>
     </row>
     <row r="185">
-      <c r="E185" s="6"/>
+      <c r="E185" s="9"/>
+      <c r="G185" s="9"/>
+      <c r="I185" s="9"/>
+      <c r="J185" s="9"/>
     </row>
     <row r="186">
-      <c r="E186" s="6"/>
+      <c r="E186" s="9"/>
+      <c r="G186" s="9"/>
+      <c r="I186" s="9"/>
+      <c r="J186" s="9"/>
     </row>
     <row r="187">
-      <c r="E187" s="6"/>
+      <c r="E187" s="9"/>
+      <c r="G187" s="9"/>
+      <c r="I187" s="9"/>
+      <c r="J187" s="9"/>
     </row>
     <row r="188">
-      <c r="E188" s="6"/>
+      <c r="E188" s="9"/>
+      <c r="G188" s="9"/>
+      <c r="I188" s="9"/>
+      <c r="J188" s="9"/>
     </row>
     <row r="189">
-      <c r="E189" s="6"/>
+      <c r="E189" s="9"/>
+      <c r="G189" s="9"/>
+      <c r="I189" s="9"/>
+      <c r="J189" s="9"/>
     </row>
     <row r="190">
-      <c r="E190" s="6"/>
+      <c r="E190" s="9"/>
+      <c r="G190" s="9"/>
+      <c r="I190" s="9"/>
+      <c r="J190" s="9"/>
     </row>
     <row r="191">
-      <c r="E191" s="6"/>
+      <c r="E191" s="9"/>
+      <c r="G191" s="9"/>
+      <c r="I191" s="9"/>
+      <c r="J191" s="9"/>
     </row>
     <row r="192">
-      <c r="E192" s="6"/>
+      <c r="E192" s="9"/>
+      <c r="G192" s="9"/>
+      <c r="I192" s="9"/>
+      <c r="J192" s="9"/>
     </row>
     <row r="193">
-      <c r="E193" s="6"/>
+      <c r="E193" s="9"/>
+      <c r="G193" s="9"/>
+      <c r="I193" s="9"/>
+      <c r="J193" s="9"/>
     </row>
     <row r="194">
-      <c r="E194" s="6"/>
+      <c r="E194" s="9"/>
+      <c r="G194" s="9"/>
+      <c r="I194" s="9"/>
+      <c r="J194" s="9"/>
     </row>
     <row r="195">
-      <c r="E195" s="6"/>
+      <c r="E195" s="9"/>
+      <c r="G195" s="9"/>
+      <c r="I195" s="9"/>
+      <c r="J195" s="9"/>
     </row>
     <row r="196">
-      <c r="E196" s="6"/>
+      <c r="E196" s="9"/>
+      <c r="G196" s="9"/>
+      <c r="I196" s="9"/>
+      <c r="J196" s="9"/>
     </row>
     <row r="197">
-      <c r="E197" s="6"/>
+      <c r="E197" s="9"/>
+      <c r="G197" s="9"/>
+      <c r="I197" s="9"/>
+      <c r="J197" s="9"/>
     </row>
     <row r="198">
-      <c r="E198" s="6"/>
+      <c r="E198" s="9"/>
+      <c r="G198" s="9"/>
+      <c r="I198" s="9"/>
+      <c r="J198" s="9"/>
     </row>
     <row r="199">
-      <c r="E199" s="6"/>
+      <c r="E199" s="9"/>
+      <c r="G199" s="9"/>
+      <c r="I199" s="9"/>
+      <c r="J199" s="9"/>
     </row>
     <row r="200">
-      <c r="E200" s="6"/>
+      <c r="E200" s="9"/>
+      <c r="G200" s="9"/>
+      <c r="I200" s="9"/>
+      <c r="J200" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CardData/BuffCard.xlsx
+++ b/CardData/BuffCard.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>1792414558057962</author>
+    <author>1792479869972825</author>
   </authors>
   <commentList>
     <comment ref="E3" authorId="0">
@@ -76,28 +76,28 @@
     <t>string</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(array#sep=_),int</t>
-  </si>
-  <si>
-    <t>(array#sep=_),int</t>
-  </si>
-  <si>
-    <t>(array#sep=_),int</t>
+    <t xml:space="preserve">(array#sep=,), (array#sep=_),int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(array#sep=,), (array#sep=_),int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(array#sep=,), (array#sep=_),int</t>
   </si>
   <si>
     <t>string</t>
@@ -150,7 +150,21 @@
     <t>5_1_13_1_0</t>
   </si>
   <si>
-    <t>null</t>
+    <t>c_0</t>
+  </si>
+  <si>
+    <t>燃心(连击)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使用时，我方能量+1
+我方主要阶段结束时，将一张能量加入手牌。
+若处于【连击】状态，再将一张能量加入手牌。</t>
+  </si>
+  <si>
+    <t>1_1_0</t>
+  </si>
+  <si>
+    <t>5_1_13_2_0</t>
   </si>
   <si>
     <t>c_0</t>
@@ -208,7 +222,7 @@
   <borders count="1">
     <border/>
   </borders>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf fontId="1" fillId="2" applyFont="1" applyFill="1">
       <alignment vertical="bottom"/>
@@ -235,6 +249,9 @@
     <xf fontId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -418,18 +435,58 @@
       <c r="I4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="7" t="s">
+    </row>
+    <row r="5" ht="38.545456" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="E5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+      <c r="C5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
     </row>
     <row r="6">
       <c r="E6" s="9"/>
